--- a/excel/Financial_Statements.xlsx
+++ b/excel/Financial_Statements.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Yellow cell = your answer goes here.</t>
   </si>
   <si>
-    <t xml:space="preserve">Worked example: Amina Stores (notes section 6). Practice: Ben's Bikes (Model Question FS.6).</t>
+    <t xml:space="preserve">Worked example: Amina Stores (notes section 6). Practice: Ben's Bikes (Model Question FS.9).</t>
   </si>
   <si>
     <t xml:space="preserve">Amina Stores: Trial balance at 31 December 2025</t>
@@ -322,7 +322,7 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: Ben's Bikes (Model Question FS.6)</t>
+    <t xml:space="preserve">Practice: Ben's Bikes (Model Question FS.9)</t>
   </si>
   <si>
     <t xml:space="preserve">Type your answers in the yellow cells. The Check column marks them.</t>
@@ -421,7 +421,7 @@
     <t xml:space="preserve">Your score (number correct)</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: Ben's Bikes (Model Question FS.6): Answers</t>
+    <t xml:space="preserve">Practice: Ben's Bikes (Model Question FS.9): Answers</t>
   </si>
   <si>
     <t xml:space="preserve">Every answer is a formula linked to the Practice sheet data.</t>
